--- a/CE国試data/CE_questions_2019.xlsx
+++ b/CE国試data/CE_questions_2019.xlsx
@@ -893,7 +893,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
@@ -2777,7 +2777,7 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
@@ -3868,7 +3868,7 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
@@ -4454,7 +4454,7 @@
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
@@ -5552,7 +5552,7 @@
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
@@ -6156,7 +6156,7 @@
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T58" t="inlineStr">
@@ -7143,7 +7143,7 @@
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T68" t="inlineStr">
@@ -7446,7 +7446,7 @@
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T71" t="inlineStr">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T95" t="inlineStr">
@@ -10206,7 +10206,7 @@
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T99" t="inlineStr">
@@ -10898,7 +10898,7 @@
       </c>
       <c r="S106" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T106" t="inlineStr">
@@ -11878,7 +11878,7 @@
       </c>
       <c r="S116" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T116" t="inlineStr">
@@ -12868,7 +12868,7 @@
       </c>
       <c r="S126" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T126" t="inlineStr">
@@ -14351,7 +14351,7 @@
       </c>
       <c r="S141" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T141" t="inlineStr">
@@ -14655,7 +14655,7 @@
       </c>
       <c r="S144" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T144" t="inlineStr">
@@ -14756,7 +14756,7 @@
       </c>
       <c r="S145" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T145" t="inlineStr">
@@ -15434,7 +15434,7 @@
       </c>
       <c r="S152" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T152" t="inlineStr">
@@ -18184,7 +18184,7 @@
       </c>
       <c r="S180" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T180" t="inlineStr">
